--- a/apps/web/public/importmallar/importmall-inkopspriser.xlsx
+++ b/apps/web/public/importmallar/importmall-inkopspriser.xlsx
@@ -58,7 +58,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Pris per grundenhet (antal 1) i leverantörens valuta, decimalkomma eller punkt, aldrig negativt; fyra decimaler sparas. Tom cell lämnar priset orört på en befintlig katalograd.</t>
+          <t xml:space="preserve">Pris per grundenhet (antal 1) i katalogradens valuta — en ny katalograd får leverantörens valuta, en befintlig behåller sin. Decimalkomma eller punkt, aldrig negativt; fyra decimaler sparas. Tom cell lämnar priset orört på en befintlig katalograd.</t>
         </r>
       </text>
     </comment>
@@ -70,7 +70,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i radens pris och staffelpris — Pris × (1 − Rabatt/100) — med en varning, eftersom katalogen saknar rabattfält. Tom cell betyder ingen rabatt.</t>
+          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i radens pris och staffelpris — Pris × (1 − Rabatt/100) — med en varning, eftersom katalogen saknar rabattfält. Skriv bara talet — 10 betyder 10 %; skriv inte procenttecken. Tom cell betyder ingen rabatt.</t>
         </r>
       </text>
     </comment>
@@ -82,7 +82,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej när kolumnen är mappad. Ja gör leverantören till artikelns huvudleverantör och tar bort markeringen från en tidigare — högst en per artikel i filen.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör leverantören till artikelns huvudleverantör och tar bort markeringen från en tidigare — högst en per artikel i filen. Tom cell tar bort markeringen från en befintlig katalograd — ta bort kolumnen för att lämna den orörd.</t>
         </r>
       </text>
     </comment>
@@ -94,7 +94,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Antalet i grundenhet där staffelpriset börjar gälla, större än 1 — ett gränsvärde på 1 eller lägre ignoreras med en varning (antal 1 är grundpriset). Är kolumnen mappad ersätts katalogradens staffel helt av filens steg (inga steg = staffeln tas bort); är den inte mappad rörs staffeln inte.</t>
+          <t xml:space="preserve">Antalet i grundenhet där staffelpriset börjar gälla, större än 1 — ett gränsvärde på 1 eller lägre ignoreras med en varning (antal 1 är grundpriset). Finns kolumnen ersätts katalogradens staffel helt av filens steg — tomma celler betyder att staffeln tas bort; ta bort kolumnen för att lämna staffeln orörd.</t>
         </r>
       </text>
     </comment>
@@ -106,7 +106,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Priset per grundenhet från och med gränsvärdet, decimalkomma eller punkt, aldrig negativt. Krävs på varje rad som har ett gränsvärde.</t>
+          <t xml:space="preserve">Priset per grundenhet från och med gränsvärdet, decimalkomma eller punkt, aldrig negativt. Krävs på varje rad som har ett gränsvärde; utan Staffel: från antal läses kolumnen inte.</t>
         </r>
       </text>
     </comment>
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -158,6 +158,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,11 +170,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1" style="4"/>
+    <col min="2" max="2" width="21" customWidth="1" style="4"/>
+    <col min="3" max="3" width="31" customWidth="1" style="4"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1" style="4"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -254,66 +255,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artikelnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PL-2-1500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leverantörsnummer</t>
+          <t xml:space="preserve">Artikelnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -323,41 +309,41 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Numret på en leverantör som redan finns i leverantörsregistret. Alla rader med samma artikel och leverantör bildar en katalograd: den första raden ger pris och övriga uppgifter, varje rad kan bära ett staffelsteg.</t>
+          <t xml:space="preserve">Numret på en artikel som redan finns i artikelregistret.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001</t>
+          <t xml:space="preserve">PL-2-1500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leverantörens artikelnummer</t>
+          <t xml:space="preserve">Leverantörsnummer</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leverantörens eget nummer på artikeln, max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Numret på en leverantör som redan finns i leverantörsregistret. Alla rader med samma artikel och leverantör bildar en katalograd: den första raden ger pris och övriga uppgifter, varje rad kan bära ett staffelsteg.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEV-4471</t>
+          <t xml:space="preserve">2001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pris</t>
+          <t xml:space="preserve">Leverantörens artikelnummer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -367,19 +353,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pris per grundenhet (antal 1) i leverantörens valuta, decimalkomma eller punkt, aldrig negativt; fyra decimaler sparas. Tom cell lämnar priset orört på en befintlig katalograd.</t>
+          <t xml:space="preserve">Leverantörens eget nummer på artikeln, max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245,00</t>
+          <t xml:space="preserve">LEV-4471</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabatt (%)</t>
+          <t xml:space="preserve">Pris</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -389,19 +375,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i radens pris och staffelpris — Pris × (1 − Rabatt/100) — med en varning, eftersom katalogen saknar rabattfält. Tom cell betyder ingen rabatt.</t>
+          <t xml:space="preserve">Pris per grundenhet (antal 1) i katalogradens valuta — en ny katalograd får leverantörens valuta, en befintlig behåller sin. Decimalkomma eller punkt, aldrig negativt; fyra decimaler sparas. Tom cell lämnar priset orört på en befintlig katalograd.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">245,00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huvudleverantör</t>
+          <t xml:space="preserve">Rabatt (%)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -411,19 +397,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej när kolumnen är mappad. Ja gör leverantören till artikelns huvudleverantör och tar bort markeringen från en tidigare — högst en per artikel i filen.</t>
+          <t xml:space="preserve">Procentavdrag från 0 upp till (men inte med) 100 som bakas in i radens pris och staffelpris — Pris × (1 − Rabatt/100) — med en varning, eftersom katalogen saknar rabattfält. Skriv bara talet — 10 betyder 10 %; skriv inte procenttecken. Tom cell betyder ingen rabatt.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Staffel: från antal</t>
+          <t xml:space="preserve">Huvudleverantör</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -433,32 +419,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antalet i grundenhet där staffelpriset börjar gälla, större än 1 — ett gränsvärde på 1 eller lägre ignoreras med en varning (antal 1 är grundpriset). Är kolumnen mappad ersätts katalogradens staffel helt av filens steg (inga steg = staffeln tas bort); är den inte mappad rörs staffeln inte.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false; tom cell betyder Nej. Ja gör leverantören till artikelns huvudleverantör och tar bort markeringen från en tidigare — högst en per artikel i filen. Tom cell tar bort markeringen från en befintlig katalograd — ta bort kolumnen för att lämna den orörd.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Staffel: från antal</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antalet i grundenhet där staffelpriset börjar gälla, större än 1 — ett gränsvärde på 1 eller lägre ignoreras med en varning (antal 1 är grundpriset). Finns kolumnen ersätts katalogradens staffel helt av filens steg — tomma celler betyder att staffeln tas bort; ta bort kolumnen för att lämna staffeln orörd.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Staffel: pris</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priset per grundenhet från och med gränsvärdet, decimalkomma eller punkt, aldrig negativt. Krävs på varje rad som har ett gränsvärde.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priset per grundenhet från och med gränsvärdet, decimalkomma eller punkt, aldrig negativt. Krävs på varje rad som har ett gränsvärde; utan Staffel: från antal läses kolumnen inte.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">219,00</t>
         </is>
